--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Unadjusted_Boot.xlsx
@@ -385,10 +385,10 @@
         <v>16.175</v>
       </c>
       <c r="C2">
-        <v>16.002</v>
+        <v>15.989</v>
       </c>
       <c r="D2">
-        <v>16.366</v>
+        <v>16.361</v>
       </c>
     </row>
     <row r="3">
@@ -399,10 +399,10 @@
         <v>11.295</v>
       </c>
       <c r="C3">
-        <v>11.129</v>
+        <v>11.126</v>
       </c>
       <c r="D3">
-        <v>11.458</v>
+        <v>11.46</v>
       </c>
     </row>
   </sheetData>
@@ -445,10 +445,10 @@
         <v>16.43</v>
       </c>
       <c r="C2">
-        <v>16.25</v>
+        <v>16.246</v>
       </c>
       <c r="D2">
-        <v>16.617</v>
+        <v>16.608</v>
       </c>
     </row>
     <row r="3">
@@ -459,10 +459,10 @@
         <v>11.473</v>
       </c>
       <c r="C3">
-        <v>11.309</v>
+        <v>11.314</v>
       </c>
       <c r="D3">
-        <v>11.624</v>
+        <v>11.633</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Unadjusted_Boot.xlsx
@@ -382,13 +382,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.175</v>
+        <v>13.875</v>
       </c>
       <c r="C2">
-        <v>15.989</v>
+        <v>13.709</v>
       </c>
       <c r="D2">
-        <v>16.361</v>
+        <v>14.048</v>
       </c>
     </row>
     <row r="3">
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11.295</v>
+        <v>7.265</v>
       </c>
       <c r="C3">
-        <v>11.126</v>
+        <v>7.12</v>
       </c>
       <c r="D3">
-        <v>11.46</v>
+        <v>7.415</v>
       </c>
     </row>
   </sheetData>
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.43</v>
+        <v>14.307</v>
       </c>
       <c r="C2">
-        <v>16.246</v>
+        <v>14.124</v>
       </c>
       <c r="D2">
-        <v>16.608</v>
+        <v>14.483</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11.473</v>
+        <v>7.492</v>
       </c>
       <c r="C3">
-        <v>11.314</v>
+        <v>7.342</v>
       </c>
       <c r="D3">
-        <v>11.633</v>
+        <v>7.641</v>
       </c>
     </row>
   </sheetData>
